--- a/Entregas.xlsx
+++ b/Entregas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78f04a1edbdcd847/Documentos/Bases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09617D3B-AE60-46BB-8F42-793221AF4AF3}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5535F19C-8BB9-4444-B024-063F7C580D39}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{11CB4283-0386-44E0-AF73-975A4BE33354}"/>
   </bookViews>
@@ -232,10 +232,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2078E04-C73F-4A4B-8DED-06D8C7D96342}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -816,10 +816,10 @@
       <c r="A24" s="4">
         <v>46183</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="11">
         <v>2</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="10">
         <v>46</v>
       </c>
     </row>
@@ -827,11 +827,22 @@
       <c r="A25" s="4">
         <v>46184</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="11">
         <v>16</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="10">
         <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>46185</v>
+      </c>
+      <c r="B26" s="15">
+        <v>11</v>
+      </c>
+      <c r="C26" s="14">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Entregas.xlsx
+++ b/Entregas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78f04a1edbdcd847/Documentos/Bases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5535F19C-8BB9-4444-B024-063F7C580D39}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08298B90-2564-4BA8-9532-B7ED5259D4F2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{11CB4283-0386-44E0-AF73-975A4BE33354}"/>
   </bookViews>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2078E04-C73F-4A4B-8DED-06D8C7D96342}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -838,11 +838,44 @@
       <c r="A26" s="4">
         <v>46185</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="11">
         <v>11</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="10">
         <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>46188</v>
+      </c>
+      <c r="B27" s="15">
+        <v>8</v>
+      </c>
+      <c r="C27" s="14">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>46189</v>
+      </c>
+      <c r="B28" s="15">
+        <v>5</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>46191</v>
+      </c>
+      <c r="B29" s="15">
+        <v>0</v>
+      </c>
+      <c r="C29" s="14">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
